--- a/tams-invest-parent/tams-invest-portfolio/src/main/resources/tpl/PtlCashFlowGapAnalysis001.xlsx
+++ b/tams-invest-parent/tams-invest-portfolio/src/main/resources/tpl/PtlCashFlowGapAnalysis001.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="1170" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -45,6 +45,10 @@
   </si>
   <si>
     <t>交易方向</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>组合系列</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -394,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17.25" customWidth="1"/>
@@ -404,9 +408,10 @@
     <col min="6" max="6" width="21.125" customWidth="1"/>
     <col min="7" max="7" width="21" customWidth="1"/>
     <col min="8" max="8" width="16.125" customWidth="1"/>
+    <col min="9" max="9" width="19.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -430,6 +435,9 @@
       </c>
       <c r="H1" t="s">
         <v>5</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
